--- a/AfterToken/Configs/GameConfig/Datas/production.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/production.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,111 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Refine Enhancement Part</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Refine parts from wood and scrap.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10004,3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>11001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Assemble Tactical Core</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Assemble a tactical core.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>11001,2;10000,1</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>11002</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Culture Gene Sample</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Culture a rare gene sample.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11002,1;10006,2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>11003</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
